--- a/UzTMK/UzTMK_BankBP_Tungsten_HMP.xlsx
+++ b/UzTMK/UzTMK_BankBP_Tungsten_HMP.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="561">
   <si>
     <t xml:space="preserve">БИЗНЕС-ПЛАН ИНВЕСТИЦИОННОГО ПРОЕКТА</t>
   </si>
@@ -286,7 +286,7 @@
     <t xml:space="preserve">- Все затраты сверх суммы кредита финансируются за счёт собственных средств заемщика.</t>
   </si>
   <si>
-    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года капитализируются в стоимость основных средств.</t>
+    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года отражаются в расходах 1-го года и оплачиваются за счёт собственных средств заемщика.</t>
   </si>
   <si>
     <t xml:space="preserve">- Резерв на непредвиденные расходы - 1% суммы кредита.</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">Приложение 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Линейный метод. Проценты льготного периода капитализированы в стоимость основных средств (МСФО IAS 23).</t>
+    <t xml:space="preserve">Линейный метод.</t>
   </si>
   <si>
     <t xml:space="preserve">ОБЪЕКТЫ АМОРТИЗАЦИИ</t>
@@ -692,12 +692,6 @@
     <t xml:space="preserve">Поддерживающие капвложения (% от первоначальной стоимости ОС)</t>
   </si>
   <si>
-    <t xml:space="preserve">Капитализированные проценты по кредиту за льготный период (1-й год)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Затраты по займам (МСФО IAS 23)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Х</t>
   </si>
   <si>
@@ -1361,7 +1355,7 @@
     <t xml:space="preserve">ФИНАНСОВЫЕ ИЗДЕРЖКИ</t>
   </si>
   <si>
-    <t xml:space="preserve">   Проценты за кредит (1-й год - капитализированы, оплачены за счёт собственных средств)</t>
+    <t xml:space="preserve">   Проценты за кредит (1-й год - за счёт собственных средств заемщика)</t>
   </si>
   <si>
     <t xml:space="preserve">ПОЛНАЯ СТОИМОСТЬ ПРОДАННОЙ ПРОДУКЦИИ</t>
@@ -1514,7 +1508,7 @@
     <t xml:space="preserve">Долг / EBITDA</t>
   </si>
   <si>
-    <t xml:space="preserve">1-й год: проценты за кредит льготного периода оплачиваются за счёт собственных средств и капитализируются в стоимость основных средств (МСФО IAS 23, Приложения 1 и 4); в отчёт о прибылях и убытках не включаются.</t>
+    <t xml:space="preserve">1-й год: проценты за кредит льготного периода отражены в расходах 1-го года и оплачиваются за счёт собственных средств заемщика (включены в стоимость проекта, Приложение 1).</t>
   </si>
   <si>
     <t xml:space="preserve">ПРЕДПОЛОЖЕНИЯ ПО РАБОЧЕМУ КАПИТАЛУ (в экв. долл. США)</t>
@@ -1634,7 +1628,7 @@
     <t xml:space="preserve">Проценты за кредит (B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период (проценты льготного периода)</t>
+    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период</t>
   </si>
   <si>
     <t xml:space="preserve">Чистые поступления наличности</t>
@@ -2167,10 +2161,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2221,6 +2211,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -3057,31 +3051,31 @@
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">ProfLoss!D22</f>
-        <v>2927686.3995105</v>
+        <v>1905807.54839819</v>
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">ProfLoss!E22</f>
-        <v>16162512.919018</v>
+        <v>16183053.1974323</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">ProfLoss!F22</f>
-        <v>20929536.151416</v>
+        <v>20950076.4298303</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">ProfLoss!G22</f>
-        <v>22836995.1406838</v>
+        <v>22857535.4190981</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">ProfLoss!H22</f>
-        <v>23547172.1401401</v>
+        <v>23567712.4185544</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">ProfLoss!I22</f>
-        <v>24271185.8423067</v>
+        <v>24291726.120721</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">ProfLoss!J22</f>
-        <v>25015910.8386623</v>
+        <v>25036451.1170767</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3093,31 +3087,31 @@
       </c>
       <c r="D41" s="14" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-25431200.0503813</v>
+        <v>-25250868.4884203</v>
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>5266470.07422887</v>
+        <v>5262845.31921458</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>14249199.4959908</v>
+        <v>14245574.7409765</v>
       </c>
       <c r="G41" s="14" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>24697202.4468361</v>
+        <v>24693577.6918218</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>25548304.3217475</v>
+        <v>25544679.5667332</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>26090594.7696718</v>
+        <v>26086970.0146575</v>
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>26645386.2688947</v>
+        <v>26641761.5138804</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3165,31 +3159,31 @@
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">CashFlow!D26</f>
-        <v>3721522.16568379</v>
+        <v>3901853.72764478</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">CashFlow!E26</f>
-        <v>833883.93856851</v>
+        <v>830259.183554219</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">CashFlow!F26</f>
-        <v>10021252.9413631</v>
+        <v>10017628.1863488</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">CashFlow!G26</f>
-        <v>20670631.1707801</v>
+        <v>20667006.4157658</v>
       </c>
       <c r="H43" s="14" t="n">
         <f aca="false">CashFlow!H26</f>
-        <v>21723108.3242633</v>
+        <v>21719483.569249</v>
       </c>
       <c r="I43" s="14" t="n">
         <f aca="false">CashFlow!I26</f>
-        <v>22465716.6006663</v>
+        <v>22462091.845652</v>
       </c>
       <c r="J43" s="14" t="n">
         <f aca="false">CashFlow!J26</f>
-        <v>23222940.828554</v>
+        <v>23219316.0735397</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3201,31 +3195,31 @@
       </c>
       <c r="D44" s="14" t="n">
         <f aca="false">CashFlow!D27</f>
-        <v>3721522.16568379</v>
+        <v>3901853.72764478</v>
       </c>
       <c r="E44" s="14" t="n">
         <f aca="false">CashFlow!E27</f>
-        <v>4555406.1042523</v>
+        <v>4732112.911199</v>
       </c>
       <c r="F44" s="14" t="n">
         <f aca="false">CashFlow!F27</f>
-        <v>14576659.0456154</v>
+        <v>14749741.0975478</v>
       </c>
       <c r="G44" s="14" t="n">
         <f aca="false">CashFlow!G27</f>
-        <v>35247290.2163954</v>
+        <v>35416747.5133135</v>
       </c>
       <c r="H44" s="14" t="n">
         <f aca="false">CashFlow!H27</f>
-        <v>56970398.5406587</v>
+        <v>57136231.0825625</v>
       </c>
       <c r="I44" s="14" t="n">
         <f aca="false">CashFlow!I27</f>
-        <v>79436115.141325</v>
+        <v>79598322.9282145</v>
       </c>
       <c r="J44" s="14" t="n">
         <f aca="false">CashFlow!J27</f>
-        <v>102659055.969879</v>
+        <v>102817639.001754</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3241,27 +3235,27 @@
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">CashFlow!E30</f>
-        <v>1.21078094278319</v>
+        <v>1.20986471302515</v>
       </c>
       <c r="F45" s="21" t="n">
         <f aca="false">CashFlow!F30</f>
-        <v>3.67124835624939</v>
+        <v>3.67028214763951</v>
       </c>
       <c r="G45" s="21" t="n">
         <f aca="false">CashFlow!G30</f>
-        <v>6.82246870059831</v>
+        <v>6.82144768568862</v>
       </c>
       <c r="H45" s="21" t="n">
         <f aca="false">CashFlow!H30</f>
-        <v>7.48688458093995</v>
+        <v>7.48580216828238</v>
       </c>
       <c r="I45" s="21" t="n">
         <f aca="false">CashFlow!I30</f>
-        <v>8.13547138288638</v>
+        <v>8.13432010264305</v>
       </c>
       <c r="J45" s="21" t="n">
         <f aca="false">CashFlow!J30</f>
-        <v>8.88281011084832</v>
+        <v>8.88157972165312</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3320,7 +3314,7 @@
       </c>
       <c r="C49" s="22" t="n">
         <f aca="false">NPV_IRR!D18</f>
-        <v>4404865.18239016</v>
+        <v>4553230.19349745</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3329,7 +3323,7 @@
       </c>
       <c r="C50" s="23" t="n">
         <f aca="false">NPV_IRR!D19</f>
-        <v>0.131878108331531</v>
+        <v>0.132548684120501</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3338,7 +3332,7 @@
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">NPV_IRR!D20</f>
-        <v>1.06698144381928</v>
+        <v>1.06940852653712</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3347,7 +3341,7 @@
       </c>
       <c r="C52" s="25" t="n">
         <f aca="false">NPV_IRR!D21</f>
-        <v>5.20836319156088</v>
+        <v>5.2019175161947</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3356,7 +3350,7 @@
       </c>
       <c r="C53" s="25" t="n">
         <f aca="false">NPV_IRR!D22</f>
-        <v>6.64390414474251</v>
+        <v>6.631859104008</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3376,7 +3370,7 @@
       </c>
       <c r="C55" s="23" t="n">
         <f aca="false">BreakPoint!C10</f>
-        <v>0.298419434889006</v>
+        <v>0.297674647890838</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3701,45 +3695,45 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>254</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="D6" s="62" t="n">
+        <v>292</v>
+      </c>
+      <c r="D6" s="61" t="n">
         <v>8388.832</v>
       </c>
-      <c r="E6" s="67" t="n">
+      <c r="E6" s="66" t="n">
         <f aca="false">IFERROR(F6/D6,0)</f>
         <v>112.587324559571</v>
       </c>
@@ -3749,15 +3743,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" s="62" t="n">
+        <v>294</v>
+      </c>
+      <c r="D7" s="61" t="n">
         <v>172529.28</v>
       </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="66" t="n">
         <f aca="false">IFERROR(F7/D7,0)</f>
         <v>0.63283143838014</v>
       </c>
@@ -3767,15 +3761,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D8" s="62" t="n">
+        <v>294</v>
+      </c>
+      <c r="D8" s="61" t="n">
         <v>4675367.2</v>
       </c>
-      <c r="E8" s="67" t="n">
+      <c r="E8" s="66" t="n">
         <f aca="false">IFERROR(F8/D8,0)</f>
         <v>0.188904906979146</v>
       </c>
@@ -3785,15 +3779,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D9" s="62" t="n">
+        <v>294</v>
+      </c>
+      <c r="D9" s="61" t="n">
         <v>18463.47195</v>
       </c>
-      <c r="E9" s="67" t="n">
+      <c r="E9" s="66" t="n">
         <f aca="false">IFERROR(F9/D9,0)</f>
         <v>0.480292439590273</v>
       </c>
@@ -3803,7 +3797,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -3814,7 +3808,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -3825,7 +3819,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -3836,11 +3830,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
+        <v>300</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="49" t="n">
         <f aca="false">SUM(F6:F12)</f>
         <v>2429940.25285387</v>
@@ -3848,10 +3842,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="F15" s="68" t="s">
-        <v>304</v>
+        <v>301</v>
+      </c>
+      <c r="F15" s="67" t="s">
+        <v>302</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>0.12</v>
@@ -3862,36 +3856,36 @@
         <v>44</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="F16" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="G16" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
+        <v>308</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C18" s="62" t="n">
+        <v>309</v>
+      </c>
+      <c r="C18" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="14" t="n">
@@ -3911,9 +3905,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C19" s="62" t="n">
+        <v>310</v>
+      </c>
+      <c r="C19" s="61" t="n">
         <v>16</v>
       </c>
       <c r="D19" s="14" t="n">
@@ -3933,9 +3927,9 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C20" s="62" t="n">
+        <v>311</v>
+      </c>
+      <c r="C20" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="14" t="n">
@@ -3955,9 +3949,9 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C21" s="62" t="n">
+        <v>312</v>
+      </c>
+      <c r="C21" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="14" t="n">
@@ -3977,9 +3971,9 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C22" s="62" t="n">
+        <v>313</v>
+      </c>
+      <c r="C22" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D22" s="14" t="n">
@@ -3999,9 +3993,9 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C23" s="62" t="n">
+        <v>314</v>
+      </c>
+      <c r="C23" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="14" t="n">
@@ -4021,9 +4015,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" s="62" t="n">
+        <v>315</v>
+      </c>
+      <c r="C24" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="14" t="n">
@@ -4043,9 +4037,9 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C25" s="62" t="n">
+        <v>316</v>
+      </c>
+      <c r="C25" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="14" t="n">
@@ -4065,9 +4059,9 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C26" s="62" t="n">
+        <v>317</v>
+      </c>
+      <c r="C26" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D26" s="14" t="n">
@@ -4087,9 +4081,9 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C27" s="62" t="n">
+        <v>318</v>
+      </c>
+      <c r="C27" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="14" t="n">
@@ -4109,9 +4103,9 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C28" s="62" t="n">
+        <v>319</v>
+      </c>
+      <c r="C28" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="14" t="n">
@@ -4131,9 +4125,9 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C29" s="62" t="n">
+        <v>320</v>
+      </c>
+      <c r="C29" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D29" s="14" t="n">
@@ -4153,9 +4147,9 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C30" s="62" t="n">
+        <v>321</v>
+      </c>
+      <c r="C30" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D30" s="14" t="n">
@@ -4175,9 +4169,9 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C31" s="62" t="n">
+        <v>322</v>
+      </c>
+      <c r="C31" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D31" s="14" t="n">
@@ -4197,9 +4191,9 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C32" s="62" t="n">
+        <v>323</v>
+      </c>
+      <c r="C32" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D32" s="14" t="n">
@@ -4219,9 +4213,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C33" s="62" t="n">
+        <v>324</v>
+      </c>
+      <c r="C33" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D33" s="14" t="n">
@@ -4241,9 +4235,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C34" s="62" t="n">
+        <v>325</v>
+      </c>
+      <c r="C34" s="61" t="n">
         <v>12</v>
       </c>
       <c r="D34" s="14" t="n">
@@ -4263,9 +4257,9 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C35" s="62" t="n">
+        <v>326</v>
+      </c>
+      <c r="C35" s="61" t="n">
         <v>10</v>
       </c>
       <c r="D35" s="14" t="n">
@@ -4285,9 +4279,9 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C36" s="62" t="n">
+        <v>327</v>
+      </c>
+      <c r="C36" s="61" t="n">
         <v>4</v>
       </c>
       <c r="D36" s="14" t="n">
@@ -4307,9 +4301,9 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C37" s="62" t="n">
+        <v>328</v>
+      </c>
+      <c r="C37" s="61" t="n">
         <v>6</v>
       </c>
       <c r="D37" s="14" t="n">
@@ -4331,7 +4325,7 @@
       <c r="B38" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C38" s="69" t="n">
+      <c r="C38" s="68" t="n">
         <f aca="false">SUM(C18:C37)</f>
         <v>114</v>
       </c>
@@ -4348,32 +4342,32 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
+        <v>329</v>
+      </c>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
       <c r="F39" s="49" t="n">
         <f aca="false">F38+G38</f>
         <v>1706938.18830986</v>
       </c>
-      <c r="G39" s="61"/>
+      <c r="G39" s="60"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
+        <v>330</v>
+      </c>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C42" s="62" t="n">
+        <v>331</v>
+      </c>
+      <c r="C42" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="14" t="n">
@@ -4393,9 +4387,9 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C43" s="62" t="n">
+        <v>332</v>
+      </c>
+      <c r="C43" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="14" t="n">
@@ -4415,9 +4409,9 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C44" s="62" t="n">
+        <v>333</v>
+      </c>
+      <c r="C44" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D44" s="14" t="n">
@@ -4437,9 +4431,9 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C45" s="62" t="n">
+        <v>334</v>
+      </c>
+      <c r="C45" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="14" t="n">
@@ -4459,9 +4453,9 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C46" s="62" t="n">
+        <v>335</v>
+      </c>
+      <c r="C46" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="14" t="n">
@@ -4481,9 +4475,9 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C47" s="62" t="n">
+        <v>336</v>
+      </c>
+      <c r="C47" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="14" t="n">
@@ -4503,9 +4497,9 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C48" s="62" t="n">
+        <v>337</v>
+      </c>
+      <c r="C48" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="14" t="n">
@@ -4525,9 +4519,9 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C49" s="62" t="n">
+        <v>338</v>
+      </c>
+      <c r="C49" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="14" t="n">
@@ -4547,9 +4541,9 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C50" s="62" t="n">
+        <v>339</v>
+      </c>
+      <c r="C50" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="14" t="n">
@@ -4569,9 +4563,9 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="C51" s="62" t="n">
+        <v>340</v>
+      </c>
+      <c r="C51" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="14" t="n">
@@ -4591,9 +4585,9 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="C52" s="62" t="n">
+        <v>341</v>
+      </c>
+      <c r="C52" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="14" t="n">
@@ -4613,9 +4607,9 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C53" s="62" t="n">
+        <v>342</v>
+      </c>
+      <c r="C53" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="14" t="n">
@@ -4635,9 +4629,9 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C54" s="62" t="n">
+        <v>343</v>
+      </c>
+      <c r="C54" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="14" t="n">
@@ -4657,9 +4651,9 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="62" t="n">
+        <v>344</v>
+      </c>
+      <c r="C55" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D55" s="14" t="n">
@@ -4679,9 +4673,9 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="C56" s="62" t="n">
+        <v>345</v>
+      </c>
+      <c r="C56" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="14" t="n">
@@ -4701,9 +4695,9 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C57" s="62" t="n">
+        <v>346</v>
+      </c>
+      <c r="C57" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="14" t="n">
@@ -4723,9 +4717,9 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C58" s="62" t="n">
+        <v>347</v>
+      </c>
+      <c r="C58" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D58" s="14" t="n">
@@ -4745,9 +4739,9 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="C59" s="62" t="n">
+        <v>348</v>
+      </c>
+      <c r="C59" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D59" s="14" t="n">
@@ -4769,7 +4763,7 @@
       <c r="B60" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C60" s="69" t="n">
+      <c r="C60" s="68" t="n">
         <f aca="false">SUM(C42:C59)</f>
         <v>26</v>
       </c>
@@ -4786,36 +4780,36 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
+        <v>329</v>
+      </c>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
       <c r="F61" s="49" t="n">
         <f aca="false">F60+G60</f>
         <v>366184.374857015</v>
       </c>
-      <c r="G61" s="61"/>
+      <c r="G61" s="60"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="C63" s="70" t="n">
+        <v>349</v>
+      </c>
+      <c r="C63" s="69" t="n">
         <f aca="false">C38+C60</f>
         <v>140</v>
       </c>
-      <c r="D63" s="65"/>
-      <c r="E63" s="65"/>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
       <c r="F63" s="17" t="n">
         <f aca="false">F39+F61</f>
         <v>2073122.56316688</v>
       </c>
-      <c r="G63" s="65"/>
+      <c r="G63" s="64"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4845,10 +4839,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4856,7 +4850,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>46</v>
@@ -4893,9 +4887,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="61"/>
+        <v>354</v>
+      </c>
+      <c r="C6" s="60"/>
       <c r="D6" s="49" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>187328.591638295</v>
@@ -4927,10 +4921,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">CostSold!D35</f>
@@ -4963,7 +4957,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="14" t="n">
@@ -4997,7 +4991,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="14" t="n">
@@ -5031,7 +5025,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="14" t="n">
@@ -5065,10 +5059,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>81202.2791382946</v>
@@ -5094,78 +5088,78 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="61"/>
+        <v>362</v>
+      </c>
+      <c r="C13" s="60"/>
       <c r="D13" s="49" t="n">
         <f aca="false">D14+D15</f>
-        <v>516650.541090088</v>
+        <v>336318.979129091</v>
       </c>
       <c r="E13" s="49" t="n">
         <f aca="false">E14+E15</f>
-        <v>2852208.16217965</v>
+        <v>2855832.91719394</v>
       </c>
       <c r="F13" s="49" t="n">
         <f aca="false">F14+F15</f>
-        <v>3693447.55613223</v>
+        <v>3697072.31114652</v>
       </c>
       <c r="G13" s="49" t="n">
         <f aca="false">G14+G15</f>
-        <v>4030057.96600302</v>
+        <v>4033682.72101731</v>
       </c>
       <c r="H13" s="49" t="n">
         <f aca="false">H14+H15</f>
-        <v>4155383.31884825</v>
+        <v>4159008.07386254</v>
       </c>
       <c r="I13" s="49" t="n">
         <f aca="false">I14+I15</f>
-        <v>4283150.44276</v>
+        <v>4286775.19777429</v>
       </c>
       <c r="J13" s="49" t="n">
         <f aca="false">J14+J15</f>
-        <v>4414572.50094041</v>
+        <v>4418197.2559547</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="14" t="n">
         <f aca="false">ProfLoss!D21</f>
-        <v>516650.541090088</v>
+        <v>336318.979129091</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">ProfLoss!E21</f>
-        <v>2852208.16217965</v>
+        <v>2855832.91719394</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">ProfLoss!F21</f>
-        <v>3693447.55613223</v>
+        <v>3697072.31114652</v>
       </c>
       <c r="G14" s="14" t="n">
         <f aca="false">ProfLoss!G21</f>
-        <v>4030057.96600302</v>
+        <v>4033682.72101731</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">ProfLoss!H21</f>
-        <v>4155383.31884825</v>
+        <v>4159008.07386254</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">ProfLoss!I21</f>
-        <v>4283150.44276</v>
+        <v>4286775.19777429</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">ProfLoss!J21</f>
-        <v>4414572.50094041</v>
+        <v>4418197.2559547</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">MAX(0,D22)</f>
@@ -5198,46 +5192,46 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="39" t="s">
-        <v>367</v>
-      </c>
-      <c r="C16" s="63"/>
+        <v>365</v>
+      </c>
+      <c r="C16" s="62"/>
       <c r="D16" s="17" t="n">
         <f aca="false">D6+D13</f>
-        <v>703979.132728382</v>
+        <v>523647.570767386</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">E6+E13</f>
-        <v>3484846.84597285</v>
+        <v>3488471.60098714</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">F6+F13</f>
-        <v>4322326.20575725</v>
+        <v>4325950.96077154</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">G6+G13</f>
-        <v>4655302.6858733</v>
+        <v>4658927.44088759</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">H6+H13</f>
-        <v>4777103.64530568</v>
+        <v>4780728.40031997</v>
       </c>
       <c r="I16" s="17" t="n">
         <f aca="false">I6+I13</f>
-        <v>4901456.24614949</v>
+        <v>4905081.00116378</v>
       </c>
       <c r="J16" s="17" t="n">
         <f aca="false">J6+J13</f>
-        <v>5029576.06875447</v>
+        <v>5033200.82376876</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="14" t="n">
@@ -5264,7 +5258,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="14" t="n">
@@ -5291,7 +5285,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="14" t="n">
@@ -5318,7 +5312,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="22" t="n">
@@ -5352,46 +5346,46 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="34" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="14" t="n">
         <f aca="false">ProfLoss!D20</f>
-        <v>3444336.94060058</v>
+        <v>2242126.52752728</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">ProfLoss!E20</f>
-        <v>19014721.0811977</v>
+        <v>19038886.1146263</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">ProfLoss!F20</f>
-        <v>24622983.7075482</v>
+        <v>24647148.7409768</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">ProfLoss!G20</f>
-        <v>26867053.1066868</v>
+        <v>26891218.1401154</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">ProfLoss!H20</f>
-        <v>27702555.4589884</v>
+        <v>27726720.492417</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">ProfLoss!I20</f>
-        <v>28554336.2850667</v>
+        <v>28578501.3184953</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">ProfLoss!J20</f>
-        <v>29430483.3396027</v>
+        <v>29454648.3730314</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="14" t="n">
@@ -5418,44 +5412,44 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="14" t="n">
         <f aca="false">D25+D26</f>
-        <v>3444336.94060058</v>
+        <v>2242126.52752728</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">E25+E26</f>
-        <v>19014721.0811977</v>
+        <v>19038886.1146263</v>
       </c>
       <c r="F27" s="14" t="n">
         <f aca="false">F25+F26</f>
-        <v>24622983.7075482</v>
+        <v>24647148.7409768</v>
       </c>
       <c r="G27" s="14" t="n">
         <f aca="false">G25+G26</f>
-        <v>26867053.1066868</v>
+        <v>26891218.1401154</v>
       </c>
       <c r="H27" s="14" t="n">
         <f aca="false">H25+H26</f>
-        <v>27702555.4589884</v>
+        <v>27726720.492417</v>
       </c>
       <c r="I27" s="14" t="n">
         <f aca="false">I25+I26</f>
-        <v>28554336.2850667</v>
+        <v>28578501.3184953</v>
       </c>
       <c r="J27" s="14" t="n">
         <f aca="false">J25+J26</f>
-        <v>29430483.3396027</v>
+        <v>29454648.3730314</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0.15</v>
@@ -5481,36 +5475,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="22" t="n">
-        <f aca="false">D27*D28</f>
-        <v>516650.541090088</v>
+        <f aca="false">MAX(0,MIN(D27,SUM($D27:D27)))*D28</f>
+        <v>336318.979129091</v>
       </c>
       <c r="E29" s="22" t="n">
-        <f aca="false">E27*E28</f>
-        <v>2852208.16217965</v>
+        <f aca="false">MAX(0,MIN(E27,SUM($D27:E27)))*E28</f>
+        <v>2855832.91719394</v>
       </c>
       <c r="F29" s="22" t="n">
-        <f aca="false">F27*F28</f>
-        <v>3693447.55613223</v>
+        <f aca="false">MAX(0,MIN(F27,SUM($D27:F27)))*F28</f>
+        <v>3697072.31114652</v>
       </c>
       <c r="G29" s="22" t="n">
-        <f aca="false">G27*G28</f>
-        <v>4030057.96600302</v>
+        <f aca="false">MAX(0,MIN(G27,SUM($D27:G27)))*G28</f>
+        <v>4033682.72101731</v>
       </c>
       <c r="H29" s="22" t="n">
-        <f aca="false">H27*H28</f>
-        <v>4155383.31884825</v>
+        <f aca="false">MAX(0,MIN(H27,SUM($D27:H27)))*H28</f>
+        <v>4159008.07386254</v>
       </c>
       <c r="I29" s="22" t="n">
-        <f aca="false">I27*I28</f>
-        <v>4283150.44276</v>
+        <f aca="false">MAX(0,MIN(I27,SUM($D27:I27)))*I28</f>
+        <v>4286775.19777429</v>
       </c>
       <c r="J29" s="22" t="n">
-        <f aca="false">J27*J28</f>
-        <v>4414572.50094041</v>
+        <f aca="false">MAX(0,MIN(J27,SUM($D27:J27)))*J28</f>
+        <v>4418197.2559547</v>
       </c>
     </row>
   </sheetData>
@@ -5553,40 +5547,40 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" s="19" t="s">
         <v>385</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">C7+C8</f>
@@ -5611,7 +5605,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">F7+G7</f>
@@ -5635,7 +5629,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">F8+G8</f>
@@ -5659,7 +5653,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">F9+G9</f>
@@ -5684,7 +5678,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">F10+G10</f>
@@ -5708,7 +5702,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">F11+G11</f>
@@ -5732,7 +5726,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">F12+G12</f>
@@ -5756,7 +5750,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">F13+G13</f>
@@ -5780,7 +5774,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">F14+G14</f>
@@ -5804,7 +5798,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">F15+G15</f>
@@ -5827,7 +5821,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">F16+G16</f>
@@ -5851,7 +5845,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">F17+G17</f>
@@ -5875,7 +5869,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">F18+G18</f>
@@ -5899,7 +5893,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">F19+G19</f>
@@ -5923,7 +5917,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C20" s="14" t="n">
         <f aca="false">F20+G20</f>
@@ -5947,11 +5941,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">F21+G21</f>
-        <v>2593626.12717861</v>
+        <v>2569461.09375</v>
       </c>
       <c r="D21" s="15" t="n">
         <f aca="false">IFERROR(F21/C21,0)</f>
@@ -5962,8 +5956,8 @@
         <v>0</v>
       </c>
       <c r="F21" s="14" t="n">
-        <f aca="false">Depreciate!I21</f>
-        <v>2593626.12717861</v>
+        <f aca="false">Depreciate!I20</f>
+        <v>2569461.09375</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>0</v>
@@ -5975,19 +5969,19 @@
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">SUM(C6:C21)-C6</f>
-        <v>285156420.695964</v>
+        <v>285132255.662535</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">IFERROR(F22/C22,0)</f>
-        <v>0.0339546503446812</v>
+        <v>0.0338727777480024</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">IFERROR(G22/C22,0)</f>
-        <v>0.966045349655319</v>
+        <v>0.966127222251998</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">SUM(F6:F21)-F6</f>
-        <v>9682386.55827227</v>
+        <v>9658221.52484367</v>
       </c>
       <c r="G22" s="17" t="n">
         <f aca="false">SUM(G6:G21)-G6</f>
@@ -5996,16 +5990,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">C22-C24</f>
-        <v>24201324.571128</v>
+        <v>24177159.5376994</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>260955096.124836</v>
@@ -6013,7 +6007,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">SalePlan!F14</f>
@@ -6022,20 +6016,20 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="C27" s="71" t="n">
+        <v>404</v>
+      </c>
+      <c r="C27" s="70" t="n">
         <f aca="false">IFERROR(C22/C26,0)</f>
-        <v>0.926074284972257</v>
+        <v>0.925995806584854</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C28" s="14" t="n">
         <f aca="false">IFERROR(C22/ProdPlan!F13,0)</f>
-        <v>107342.902577062</v>
+        <v>107333.80600886</v>
       </c>
     </row>
   </sheetData>
@@ -6065,10 +6059,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6113,10 +6107,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">ProdPlan!D11</f>
@@ -6149,12 +6143,12 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="34" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -6183,7 +6177,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>34</v>
@@ -6212,7 +6206,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
@@ -6241,7 +6235,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
@@ -6270,7 +6264,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
@@ -6299,7 +6293,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
@@ -6328,7 +6322,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -6357,43 +6351,43 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="14" t="n">
-        <f aca="false">Depreciate!$G$22</f>
-        <v>620914.297791676</v>
+        <f aca="false">Depreciate!$G$21</f>
+        <v>614873.039434524</v>
       </c>
       <c r="E16" s="14" t="n">
-        <f aca="false">Depreciate!$H$22</f>
-        <v>2535269.60932147</v>
+        <f aca="false">Depreciate!$H$21</f>
+        <v>2511104.57589286</v>
       </c>
       <c r="F16" s="14" t="n">
-        <f aca="false">Depreciate!$I$22</f>
-        <v>2582911.84146432</v>
+        <f aca="false">Depreciate!$I$21</f>
+        <v>2558746.80803571</v>
       </c>
       <c r="G16" s="14" t="n">
-        <f aca="false">Depreciate!$J$22</f>
-        <v>2630554.07360718</v>
+        <f aca="false">Depreciate!$J$21</f>
+        <v>2606389.04017857</v>
       </c>
       <c r="H16" s="14" t="n">
-        <f aca="false">Depreciate!$K$22</f>
-        <v>2678196.30575004</v>
+        <f aca="false">Depreciate!$K$21</f>
+        <v>2654031.27232143</v>
       </c>
       <c r="I16" s="14" t="n">
-        <f aca="false">Depreciate!$L$22</f>
-        <v>2725838.53789289</v>
+        <f aca="false">Depreciate!$L$21</f>
+        <v>2701673.50446428</v>
       </c>
       <c r="J16" s="14" t="n">
-        <f aca="false">Depreciate!$M$22</f>
-        <v>2773480.77003575</v>
+        <f aca="false">Depreciate!$M$21</f>
+        <v>2749315.73660714</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>34</v>
@@ -6422,7 +6416,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -6451,7 +6445,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -6479,44 +6473,44 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="72" t="s">
-        <v>423</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="71" t="s">
+        <v>421</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="49" t="n">
         <f aca="false">SUM(D9:D19)</f>
-        <v>27518781.9412815</v>
+        <v>27512740.6829243</v>
       </c>
       <c r="E20" s="49" t="n">
         <f aca="false">SUM(E9:E19)</f>
-        <v>222916342.316811</v>
+        <v>222892177.283382</v>
       </c>
       <c r="F20" s="49" t="n">
         <f aca="false">SUM(F9:F19)</f>
-        <v>273588570.94625</v>
+        <v>273564405.912822</v>
       </c>
       <c r="G20" s="49" t="n">
         <f aca="false">SUM(G9:G19)</f>
-        <v>279598321.726727</v>
+        <v>279574156.693299</v>
       </c>
       <c r="H20" s="49" t="n">
         <f aca="false">SUM(H9:H19)</f>
-        <v>285739254.847239</v>
+        <v>285715089.81381</v>
       </c>
       <c r="I20" s="49" t="n">
         <f aca="false">SUM(I9:I19)</f>
-        <v>292014240.367295</v>
+        <v>291990075.333866</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">SUM(J9:J19)</f>
-        <v>298426227.439684</v>
+        <v>298402062.406256</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
@@ -6544,47 +6538,47 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="C22" s="60" t="s">
+      <c r="B22" s="71" t="s">
+        <v>423</v>
+      </c>
+      <c r="C22" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="49" t="n">
         <f aca="false">D20+D21</f>
-        <v>21093700.036657</v>
+        <v>21087658.7782998</v>
       </c>
       <c r="E22" s="49" t="n">
         <f aca="false">E20+E21</f>
-        <v>217265749.004587</v>
+        <v>217241583.971158</v>
       </c>
       <c r="F22" s="49" t="n">
         <f aca="false">F20+F21</f>
-        <v>270814621.006673</v>
+        <v>270790455.973244</v>
       </c>
       <c r="G22" s="49" t="n">
         <f aca="false">G20+G21</f>
-        <v>279271630.847367</v>
+        <v>279247465.813938</v>
       </c>
       <c r="H22" s="49" t="n">
         <f aca="false">H20+H21</f>
-        <v>285405375.894452</v>
+        <v>285381210.861023</v>
       </c>
       <c r="I22" s="49" t="n">
         <f aca="false">I20+I21</f>
-        <v>291673016.077546</v>
+        <v>291648851.044117</v>
       </c>
       <c r="J22" s="49" t="n">
         <f aca="false">J20+J21</f>
-        <v>298077496.215561</v>
+        <v>298053331.182133</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>0.952114613686227</v>
@@ -6610,84 +6604,84 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">D22*D23</f>
-        <v>20083620.0616148</v>
+        <v>20077868.0912479</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">E22*E23</f>
-        <v>208886891.028481</v>
+        <v>208863657.920052</v>
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">F22*F23</f>
-        <v>260771142.898836</v>
+        <v>260747874.054037</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">G22*G23</f>
-        <v>268882462.667563</v>
+        <v>268859196.596179</v>
       </c>
       <c r="H24" s="14" t="n">
         <f aca="false">H22*H23</f>
-        <v>274755960.337592</v>
+        <v>274732696.981233</v>
       </c>
       <c r="I24" s="14" t="n">
         <f aca="false">I22*I23</f>
-        <v>280757669.167198</v>
+        <v>280734408.467418</v>
       </c>
       <c r="J24" s="14" t="n">
         <f aca="false">J22*J23</f>
-        <v>286890409.252092</v>
+        <v>286867151.151705</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">D22-D24</f>
-        <v>1010079.97504217</v>
+        <v>1009790.68705191</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">E22-E24</f>
-        <v>8378857.97610548</v>
+        <v>8377926.05110574</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">F22-F24</f>
-        <v>10043478.1078369</v>
+        <v>10042581.9192068</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">G22-G24</f>
-        <v>10389168.1798042</v>
+        <v>10388269.2177593</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">H22-H24</f>
-        <v>10649415.5568596</v>
+        <v>10648513.8797901</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">I22-I24</f>
-        <v>10915346.9103482</v>
+        <v>10914442.5766991</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">J22-J24</f>
-        <v>11187086.9634694</v>
+        <v>11186180.0304272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>34</v>
@@ -6716,43 +6710,43 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="14" t="n">
-        <f aca="false">Depreciate!$G$23</f>
+        <f aca="false">Depreciate!$G$22</f>
         <v>2678.57142857143</v>
       </c>
       <c r="E29" s="14" t="n">
-        <f aca="false">Depreciate!$H$23</f>
+        <f aca="false">Depreciate!$H$22</f>
         <v>10714.2857142857</v>
       </c>
       <c r="F29" s="14" t="n">
-        <f aca="false">Depreciate!$I$23</f>
+        <f aca="false">Depreciate!$I$22</f>
         <v>10714.2857142857</v>
       </c>
       <c r="G29" s="14" t="n">
-        <f aca="false">Depreciate!$J$23</f>
+        <f aca="false">Depreciate!$J$22</f>
         <v>10714.2857142857</v>
       </c>
       <c r="H29" s="14" t="n">
-        <f aca="false">Depreciate!$K$23</f>
+        <f aca="false">Depreciate!$K$22</f>
         <v>10714.2857142857</v>
       </c>
       <c r="I29" s="14" t="n">
-        <f aca="false">Depreciate!$L$23</f>
+        <f aca="false">Depreciate!$L$22</f>
         <v>8035.71428571429</v>
       </c>
       <c r="J29" s="14" t="n">
-        <f aca="false">Depreciate!$M$23</f>
+        <f aca="false">Depreciate!$M$22</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>34</v>
@@ -6781,7 +6775,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>34</v>
@@ -6809,10 +6803,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="72" t="s">
-        <v>434</v>
-      </c>
-      <c r="C32" s="60" t="s">
+      <c r="B32" s="71" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="49" t="n">
@@ -6846,12 +6840,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="34" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>34</v>
@@ -6880,7 +6874,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>34</v>
@@ -6909,7 +6903,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>34</v>
@@ -6938,7 +6932,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>34</v>
@@ -6967,7 +6961,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>34</v>
@@ -6995,10 +6989,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="72" t="s">
-        <v>438</v>
-      </c>
-      <c r="C40" s="60" t="s">
+      <c r="B40" s="71" t="s">
+        <v>436</v>
+      </c>
+      <c r="C40" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="49" t="n">
@@ -7032,18 +7026,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="34" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>0</v>
+        <f aca="false">LOANS!$C$106</f>
+        <v>1208251.67143046</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">LOANS!$D$106</f>
@@ -7072,74 +7067,74 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="39" t="s">
-        <v>441</v>
-      </c>
-      <c r="C45" s="63" t="s">
+        <v>439</v>
+      </c>
+      <c r="C45" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D45" s="17" t="n">
         <f aca="false">D22+D32+D40+D43</f>
-        <v>24886913.0593994</v>
+        <v>26089123.4724727</v>
       </c>
       <c r="E45" s="17" t="n">
         <f aca="false">E22+E32+E40+E43</f>
-        <v>228390843.418802</v>
+        <v>228366678.385374</v>
       </c>
       <c r="F45" s="17" t="n">
         <f aca="false">F22+F32+F40+F43</f>
-        <v>283296613.373702</v>
+        <v>283272448.340273</v>
       </c>
       <c r="G45" s="17" t="n">
         <f aca="false">G22+G32+G40+G43</f>
-        <v>291809343.393313</v>
+        <v>291785178.359885</v>
       </c>
       <c r="H45" s="17" t="n">
         <f aca="false">H22+H32+H40+H43</f>
-        <v>297984344.541012</v>
+        <v>297960179.507583</v>
       </c>
       <c r="I45" s="17" t="n">
         <f aca="false">I22+I32+I40+I43</f>
-        <v>304297144.214933</v>
+        <v>304272979.181505</v>
       </c>
       <c r="J45" s="17" t="n">
         <f aca="false">J22+J32+J40+J43</f>
-        <v>310744967.660397</v>
+        <v>310720802.626969</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D46" s="14" t="n">
         <f aca="false">IFERROR(D45/(ProdPlan!D15+ProdPlan!D16),0)</f>
-        <v>99547.6522375977</v>
+        <v>104356.493889891</v>
       </c>
       <c r="E46" s="14" t="n">
         <f aca="false">IFERROR(E45/(ProdPlan!E15+ProdPlan!E16),0)</f>
-        <v>106024.879437731</v>
+        <v>106013.661410259</v>
       </c>
       <c r="F46" s="14" t="n">
         <f aca="false">IFERROR(F45/(ProdPlan!F15+ProdPlan!F16),0)</f>
-        <v>107992.714644977</v>
+        <v>107983.502930342</v>
       </c>
       <c r="G46" s="14" t="n">
         <f aca="false">IFERROR(G45/(ProdPlan!G15+ProdPlan!G16),0)</f>
-        <v>109847.296590745</v>
+        <v>109838.200022543</v>
       </c>
       <c r="H46" s="14" t="n">
         <f aca="false">IFERROR(H45/(ProdPlan!H15+ProdPlan!H16),0)</f>
-        <v>112171.784129875</v>
+        <v>112162.687561673</v>
       </c>
       <c r="I46" s="14" t="n">
         <f aca="false">IFERROR(I45/(ProdPlan!I15+ProdPlan!I16),0)</f>
-        <v>114548.143879139</v>
+        <v>114539.047310937</v>
       </c>
       <c r="J46" s="14" t="n">
         <f aca="false">IFERROR(J45/(ProdPlan!J15+ProdPlan!J16),0)</f>
-        <v>116975.331323319</v>
+        <v>116966.234755117</v>
       </c>
     </row>
   </sheetData>
@@ -7181,46 +7176,46 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="59" t="n">
+      <c r="C5" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$28</f>
         <v>84</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" s="59" t="n">
+        <v>444</v>
+      </c>
+      <c r="C6" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$29</f>
         <v>12</v>
       </c>
       <c r="D6" s="73" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" s="59" t="n">
+        <v>445</v>
+      </c>
+      <c r="C7" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$30</f>
         <v>12</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7232,12 +7227,12 @@
         <v>0.07</v>
       </c>
       <c r="D8" s="73" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$26</f>
@@ -7249,7 +7244,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C10" s="74" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$31</f>
@@ -7259,31 +7254,31 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="C11" s="59" t="n">
+        <v>449</v>
+      </c>
+      <c r="C11" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$32</f>
         <v>360</v>
       </c>
       <c r="D11" s="73" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="C12" s="59" t="n">
+        <v>451</v>
+      </c>
+      <c r="C12" s="72" t="n">
         <f aca="false">C5-C6</f>
         <v>72</v>
       </c>
       <c r="D12" s="73" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C13" s="30" t="n">
         <f aca="false">C9/C12</f>
@@ -7295,28 +7290,28 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>458</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>127</v>
       </c>
       <c r="E15" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>459</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="H15" s="19" t="s">
         <v>460</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10110,7 +10105,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="34" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10141,7 +10136,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C104" s="14" t="n">
         <f aca="false">$C$9</f>
@@ -10201,7 +10196,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="13" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C106" s="14" t="n">
         <f aca="false">SUMIF($H$16:$H$99,1,$E$16:$E$99)</f>
@@ -10234,7 +10229,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="26" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C107" s="14" t="n">
         <f aca="false">C105+C106</f>
@@ -10267,7 +10262,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="26" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C108" s="14" t="n">
         <f aca="false">$C$9-SUM($C$105:C105)</f>
@@ -10325,10 +10320,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10373,7 +10368,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>34</v>
@@ -10409,7 +10404,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -10445,7 +10440,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -10481,7 +10476,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -10516,10 +10511,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="72" t="s">
-        <v>473</v>
-      </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="71" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="49" t="n">
@@ -10553,151 +10548,151 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">CostSold!D22</f>
-        <v>21093700.036657</v>
+        <v>21087658.7782998</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">CostSold!E22</f>
-        <v>217265749.004587</v>
+        <v>217241583.971158</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">CostSold!F22</f>
-        <v>270814621.006673</v>
+        <v>270790455.973244</v>
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">CostSold!G22</f>
-        <v>279271630.847367</v>
+        <v>279247465.813938</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">CostSold!H22</f>
-        <v>285405375.894452</v>
+        <v>285381210.861023</v>
       </c>
       <c r="I11" s="14" t="n">
         <f aca="false">CostSold!I22</f>
-        <v>291673016.077546</v>
+        <v>291648851.044117</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">CostSold!J22</f>
-        <v>298077496.215561</v>
+        <v>298053331.182133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">CostSold!D24</f>
-        <v>20083620.0616148</v>
+        <v>20077868.0912479</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">CostSold!E24</f>
-        <v>208886891.028481</v>
+        <v>208863657.920052</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">CostSold!F24</f>
-        <v>260771142.898836</v>
+        <v>260747874.054037</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">CostSold!G24</f>
-        <v>268882462.667563</v>
+        <v>268859196.596179</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">CostSold!H24</f>
-        <v>274755960.337592</v>
+        <v>274732696.981233</v>
       </c>
       <c r="I12" s="14" t="n">
         <f aca="false">CostSold!I24</f>
-        <v>280757669.167198</v>
+        <v>280734408.467418</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">CostSold!J24</f>
-        <v>286890409.252092</v>
+        <v>286867151.151705</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">CostSold!D25</f>
-        <v>1010079.97504217</v>
+        <v>1009790.68705191</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">CostSold!E25</f>
-        <v>8378857.97610548</v>
+        <v>8377926.05110574</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">CostSold!F25</f>
-        <v>10043478.1078369</v>
+        <v>10042581.9192068</v>
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">CostSold!G25</f>
-        <v>10389168.1798042</v>
+        <v>10388269.2177593</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">CostSold!H25</f>
-        <v>10649415.5568596</v>
+        <v>10648513.8797901</v>
       </c>
       <c r="I13" s="14" t="n">
         <f aca="false">CostSold!I25</f>
-        <v>10915346.9103482</v>
+        <v>10914442.5766991</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">CostSold!J25</f>
-        <v>11187086.9634694</v>
+        <v>11186180.0304272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="72" t="s">
-        <v>476</v>
-      </c>
-      <c r="C14" s="60" t="s">
+      <c r="B14" s="71" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="49" t="n">
         <f aca="false">D10-D11</f>
-        <v>7237549.96334301</v>
+        <v>7243591.22170016</v>
       </c>
       <c r="E14" s="49" t="n">
         <f aca="false">E10-E11</f>
-        <v>30139815.4954135</v>
+        <v>30163980.5288421</v>
       </c>
       <c r="F14" s="49" t="n">
         <f aca="false">F10-F11</f>
-        <v>37104976.0745774</v>
+        <v>37129141.108006</v>
       </c>
       <c r="G14" s="49" t="n">
         <f aca="false">G10-G11</f>
-        <v>39404765.6526332</v>
+        <v>39428930.6860618</v>
       </c>
       <c r="H14" s="49" t="n">
         <f aca="false">H10-H11</f>
-        <v>40281524.1055484</v>
+        <v>40305689.1389771</v>
       </c>
       <c r="I14" s="49" t="n">
         <f aca="false">I10-I11</f>
-        <v>41178464.4224542</v>
+        <v>41202629.4558829</v>
       </c>
       <c r="J14" s="49" t="n">
         <f aca="false">J10-J11</f>
-        <v>42097954.7844388</v>
+        <v>42122119.8178674</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -10733,7 +10728,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
@@ -10768,51 +10763,51 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="72" t="s">
-        <v>479</v>
-      </c>
-      <c r="C17" s="60" t="s">
+      <c r="B17" s="71" t="s">
+        <v>477</v>
+      </c>
+      <c r="C17" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="49" t="n">
         <f aca="false">D14-D15-D16</f>
-        <v>3444336.94060058</v>
+        <v>3450378.19895774</v>
       </c>
       <c r="E17" s="49" t="n">
         <f aca="false">E14-E15-E16</f>
-        <v>20133503.2795458</v>
+        <v>20157668.3129744</v>
       </c>
       <c r="F17" s="49" t="n">
         <f aca="false">F14-F15-F16</f>
-        <v>25537126.3248637</v>
+        <v>25561291.3582923</v>
       </c>
       <c r="G17" s="49" t="n">
         <f aca="false">G14-G15-G16</f>
-        <v>27579820.4454306</v>
+        <v>27603985.4788592</v>
       </c>
       <c r="H17" s="49" t="n">
         <f aca="false">H14-H15-H16</f>
-        <v>28213947.5191604</v>
+        <v>28238112.552589</v>
       </c>
       <c r="I17" s="49" t="n">
         <f aca="false">I14-I15-I16</f>
-        <v>28865410.5167599</v>
+        <v>28889575.5501885</v>
       </c>
       <c r="J17" s="49" t="n">
         <f aca="false">J14-J15-J16</f>
-        <v>29539124.8426313</v>
+        <v>29563289.8760599</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="14" t="n">
         <f aca="false">D19</f>
-        <v>0</v>
+        <v>1208251.67143046</v>
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">E19</f>
@@ -10841,14 +10836,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">CostSold!D43</f>
-        <v>0</v>
+        <v>1208251.67143046</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">CostSold!E43</f>
@@ -10876,188 +10871,188 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="72" t="s">
-        <v>482</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="71" t="s">
+        <v>480</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="49" t="n">
         <f aca="false">D17-D18</f>
-        <v>3444336.94060058</v>
+        <v>2242126.52752728</v>
       </c>
       <c r="E20" s="49" t="n">
         <f aca="false">E17-E18</f>
-        <v>19014721.0811977</v>
+        <v>19038886.1146263</v>
       </c>
       <c r="F20" s="49" t="n">
         <f aca="false">F17-F18</f>
-        <v>24622983.7075482</v>
+        <v>24647148.7409768</v>
       </c>
       <c r="G20" s="49" t="n">
         <f aca="false">G17-G18</f>
-        <v>26867053.1066868</v>
+        <v>26891218.1401154</v>
       </c>
       <c r="H20" s="49" t="n">
         <f aca="false">H17-H18</f>
-        <v>27702555.4589884</v>
+        <v>27726720.492417</v>
       </c>
       <c r="I20" s="49" t="n">
         <f aca="false">I17-I18</f>
-        <v>28554336.2850667</v>
+        <v>28578501.3184953</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">J17-J18</f>
-        <v>29430483.3396027</v>
+        <v>29454648.3730314</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">Taxes!D29</f>
-        <v>516650.541090088</v>
+        <v>336318.979129091</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">Taxes!E29</f>
-        <v>2852208.16217965</v>
+        <v>2855832.91719394</v>
       </c>
       <c r="F21" s="14" t="n">
         <f aca="false">Taxes!F29</f>
-        <v>3693447.55613223</v>
+        <v>3697072.31114652</v>
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">Taxes!G29</f>
-        <v>4030057.96600302</v>
+        <v>4033682.72101731</v>
       </c>
       <c r="H21" s="14" t="n">
         <f aca="false">Taxes!H29</f>
-        <v>4155383.31884825</v>
+        <v>4159008.07386254</v>
       </c>
       <c r="I21" s="14" t="n">
         <f aca="false">Taxes!I29</f>
-        <v>4283150.44276</v>
+        <v>4286775.19777429</v>
       </c>
       <c r="J21" s="14" t="n">
         <f aca="false">Taxes!J29</f>
-        <v>4414572.50094041</v>
+        <v>4418197.2559547</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="39" t="s">
-        <v>484</v>
-      </c>
-      <c r="C22" s="63" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">D20-D21</f>
-        <v>2927686.3995105</v>
+        <v>1905807.54839819</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">E20-E21</f>
-        <v>16162512.919018</v>
+        <v>16183053.1974323</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">F20-F21</f>
-        <v>20929536.151416</v>
+        <v>20950076.4298303</v>
       </c>
       <c r="G22" s="17" t="n">
         <f aca="false">G20-G21</f>
-        <v>22836995.1406838</v>
+        <v>22857535.4190981</v>
       </c>
       <c r="H22" s="17" t="n">
         <f aca="false">H20-H21</f>
-        <v>23547172.1401401</v>
+        <v>23567712.4185544</v>
       </c>
       <c r="I22" s="17" t="n">
         <f aca="false">I20-I21</f>
-        <v>24271185.8423067</v>
+        <v>24291726.120721</v>
       </c>
       <c r="J22" s="17" t="n">
         <f aca="false">J20-J21</f>
-        <v>25015910.8386623</v>
+        <v>25036451.1170767</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="34" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D25" s="15" t="n">
         <f aca="false">IFERROR(D14/D10,0)</f>
-        <v>0.255461723832976</v>
+        <v>0.255674960395329</v>
       </c>
       <c r="E25" s="15" t="n">
         <f aca="false">IFERROR(E14/E10,0)</f>
-        <v>0.121823514989751</v>
+        <v>0.121921188756618</v>
       </c>
       <c r="F25" s="15" t="n">
         <f aca="false">IFERROR(F14/F10,0)</f>
-        <v>0.120502158441012</v>
+        <v>0.120580636828415</v>
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">IFERROR(G14/G10,0)</f>
-        <v>0.123651346900533</v>
+        <v>0.123727176280098</v>
       </c>
       <c r="H25" s="15" t="n">
         <f aca="false">IFERROR(H14/H10,0)</f>
-        <v>0.123681744969013</v>
+        <v>0.123755942099535</v>
       </c>
       <c r="I25" s="15" t="n">
         <f aca="false">IFERROR(I14/I10,0)</f>
-        <v>0.123714229423276</v>
+        <v>0.123786829471179</v>
       </c>
       <c r="J25" s="15" t="n">
         <f aca="false">IFERROR(J14/J10,0)</f>
-        <v>0.123753653183042</v>
+        <v>0.123824690153398</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D26" s="15" t="n">
         <f aca="false">IFERROR(D22/D10,0)</f>
-        <v>0.103337706578795</v>
+        <v>0.0672687420568519</v>
       </c>
       <c r="E26" s="15" t="n">
         <f aca="false">IFERROR(E22/E10,0)</f>
-        <v>0.065328008897787</v>
+        <v>0.0654110315996241</v>
       </c>
       <c r="F26" s="15" t="n">
         <f aca="false">IFERROR(F22/F10,0)</f>
-        <v>0.0679707831193782</v>
+        <v>0.0680374897486704</v>
       </c>
       <c r="G26" s="15" t="n">
         <f aca="false">IFERROR(G22/G10,0)</f>
-        <v>0.0716620226395831</v>
+        <v>0.0717264776122134</v>
       </c>
       <c r="H26" s="15" t="n">
         <f aca="false">IFERROR(H22/H10,0)</f>
-        <v>0.0723000284633496</v>
+        <v>0.0723630960242933</v>
       </c>
       <c r="I26" s="15" t="n">
         <f aca="false">IFERROR(I22/I10,0)</f>
-        <v>0.0729189661582613</v>
+        <v>0.0729806761989781</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">IFERROR(J22/J10,0)</f>
-        <v>0.0735382602275504</v>
+        <v>0.0735986416523533</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11068,40 +11063,40 @@
         <v>34</v>
       </c>
       <c r="D27" s="14" t="n">
-        <f aca="false">D17+Depreciate!$G$21</f>
+        <f aca="false">D17+Depreciate!$G$20</f>
         <v>4067929.80982083</v>
       </c>
       <c r="E27" s="14" t="n">
-        <f aca="false">E17+Depreciate!$H$21</f>
+        <f aca="false">E17+Depreciate!$H$20</f>
         <v>22679487.1745815</v>
       </c>
       <c r="F27" s="14" t="n">
-        <f aca="false">F17+Depreciate!$I$21</f>
+        <f aca="false">F17+Depreciate!$I$20</f>
         <v>28130752.4520423</v>
       </c>
       <c r="G27" s="14" t="n">
-        <f aca="false">G17+Depreciate!$J$21</f>
+        <f aca="false">G17+Depreciate!$J$20</f>
         <v>30221088.804752</v>
       </c>
       <c r="H27" s="14" t="n">
-        <f aca="false">H17+Depreciate!$K$21</f>
+        <f aca="false">H17+Depreciate!$K$20</f>
         <v>30902858.1106247</v>
       </c>
       <c r="I27" s="14" t="n">
-        <f aca="false">I17+Depreciate!$L$21</f>
+        <f aca="false">I17+Depreciate!$L$20</f>
         <v>31599284.7689385</v>
       </c>
       <c r="J27" s="14" t="n">
-        <f aca="false">J17+Depreciate!$M$21</f>
+        <f aca="false">J17+Depreciate!$M$20</f>
         <v>32312605.612667</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">IFERROR(D27/D10,0)</f>
@@ -11134,38 +11129,38 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21" t="n">
         <f aca="false">IF(D19&gt;0,D17/D19,"-")</f>
-        <v>-</v>
+        <v>2.85567839924674</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">IF(E19&gt;0,E17/E19,"-")</f>
-        <v>17.9959095785335</v>
+        <v>18.0175089867689</v>
       </c>
       <c r="F29" s="21" t="n">
         <f aca="false">IF(F19&gt;0,F17/F19,"-")</f>
-        <v>27.9356041837939</v>
+        <v>27.9620388264535</v>
       </c>
       <c r="G29" s="21" t="n">
         <f aca="false">IF(G19&gt;0,G17/G19,"-")</f>
-        <v>38.6940014592124</v>
+        <v>38.7279045747384</v>
       </c>
       <c r="H29" s="21" t="n">
         <f aca="false">IF(H19&gt;0,H17/H19,"-")</f>
-        <v>55.1708751787606</v>
+        <v>55.2181286175811</v>
       </c>
       <c r="I29" s="21" t="n">
         <f aca="false">IF(I19&gt;0,I17/I19,"-")</f>
-        <v>92.7926763963675</v>
+        <v>92.870358926666</v>
       </c>
       <c r="J29" s="21" t="n">
         <f aca="false">IF(J19&gt;0,J17/J19,"-")</f>
-        <v>271.895399264405</v>
+        <v>272.117828379936</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11206,7 +11201,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>61</v>
@@ -11242,7 +11237,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -11283,90 +11278,90 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="C5" s="59" t="n">
+        <v>494</v>
+      </c>
+      <c r="C5" s="72" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="C6" s="59" t="n">
+        <v>495</v>
+      </c>
+      <c r="C6" s="72" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>498</v>
-      </c>
-      <c r="C7" s="59" t="n">
+        <v>496</v>
+      </c>
+      <c r="C7" s="72" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C8" s="59" t="n">
+        <v>497</v>
+      </c>
+      <c r="C8" s="72" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="C9" s="59" t="n">
+        <v>498</v>
+      </c>
+      <c r="C9" s="72" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="C10" s="59" t="n">
+        <v>499</v>
+      </c>
+      <c r="C10" s="72" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="C11" s="59" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" s="72" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C12" s="59" t="n">
+        <v>501</v>
+      </c>
+      <c r="C12" s="72" t="n">
         <v>540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="19" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>46</v>
@@ -11403,7 +11398,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0</v>
@@ -11432,7 +11427,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>0</v>
@@ -11461,7 +11456,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>0</v>
@@ -11490,7 +11485,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C19" s="49" t="n">
         <v>0</v>
@@ -11526,7 +11521,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>0</v>
@@ -11555,7 +11550,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
@@ -11584,7 +11579,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C22" s="49" t="n">
         <v>0</v>
@@ -11620,7 +11615,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>0</v>
@@ -11656,7 +11651,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="26" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="n">
@@ -11690,7 +11685,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="n">
@@ -11717,7 +11712,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="49" t="n">
@@ -11751,7 +11746,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -11792,15 +11787,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11845,7 +11840,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>34</v>
@@ -11881,7 +11876,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -11917,7 +11912,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -11953,7 +11948,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -11988,10 +11983,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="72" t="s">
-        <v>522</v>
-      </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="71" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="49" t="n">
@@ -12025,79 +12020,79 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">-ProfLoss!D11</f>
-        <v>-21093700.036657</v>
+        <v>-21087658.7782998</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">-ProfLoss!E11</f>
-        <v>-217265749.004587</v>
+        <v>-217241583.971158</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">-ProfLoss!F11</f>
-        <v>-270814621.006673</v>
+        <v>-270790455.973244</v>
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">-ProfLoss!G11</f>
-        <v>-279271630.847367</v>
+        <v>-279247465.813938</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">-ProfLoss!H11</f>
-        <v>-285405375.894452</v>
+        <v>-285381210.861023</v>
       </c>
       <c r="I11" s="14" t="n">
         <f aca="false">-ProfLoss!I11</f>
-        <v>-291673016.077546</v>
+        <v>-291648851.044117</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">-ProfLoss!J11</f>
-        <v>-298077496.215561</v>
+        <v>-298053331.182133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="72" t="s">
-        <v>523</v>
-      </c>
-      <c r="C12" s="60" t="s">
+      <c r="B12" s="71" t="s">
+        <v>521</v>
+      </c>
+      <c r="C12" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="49" t="n">
         <f aca="false">D10+D11</f>
-        <v>-21042962.1253518</v>
+        <v>-21036920.8669946</v>
       </c>
       <c r="E12" s="49" t="n">
         <f aca="false">E10+E11</f>
-        <v>15579006.5572405</v>
+        <v>15603171.5906691</v>
       </c>
       <c r="F12" s="49" t="n">
         <f aca="false">F10+F11</f>
-        <v>26916870.6746581</v>
+        <v>26941035.7080867</v>
       </c>
       <c r="G12" s="49" t="n">
         <f aca="false">G10+G11</f>
-        <v>37910937.2607203</v>
+        <v>37935102.2941489</v>
       </c>
       <c r="H12" s="49" t="n">
         <f aca="false">H10+H11</f>
-        <v>39082353.6355195</v>
+        <v>39106518.6689481</v>
       </c>
       <c r="I12" s="49" t="n">
         <f aca="false">I10+I11</f>
-        <v>39952924.8659475</v>
+        <v>39977089.8993761</v>
       </c>
       <c r="J12" s="49" t="n">
         <f aca="false">J10+J11</f>
-        <v>40845307.9416069</v>
+        <v>40869472.9750355</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
@@ -12133,7 +12128,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
@@ -12169,7 +12164,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -12199,115 +12194,115 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="14" t="n">
         <f aca="false">-ProfLoss!D21</f>
-        <v>-516650.541090088</v>
+        <v>-336318.979129091</v>
       </c>
       <c r="E16" s="14" t="n">
         <f aca="false">-ProfLoss!E21</f>
-        <v>-2852208.16217965</v>
+        <v>-2855832.91719394</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">-ProfLoss!F21</f>
-        <v>-3693447.55613223</v>
+        <v>-3697072.31114652</v>
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">-ProfLoss!G21</f>
-        <v>-4030057.96600302</v>
+        <v>-4033682.72101731</v>
       </c>
       <c r="H16" s="14" t="n">
         <f aca="false">-ProfLoss!H21</f>
-        <v>-4155383.31884825</v>
+        <v>-4159008.07386254</v>
       </c>
       <c r="I16" s="14" t="n">
         <f aca="false">-ProfLoss!I21</f>
-        <v>-4283150.44276</v>
+        <v>-4286775.19777429</v>
       </c>
       <c r="J16" s="14" t="n">
         <f aca="false">-ProfLoss!J21</f>
-        <v>-4414572.50094041</v>
+        <v>-4418197.2559547</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="14" t="n">
-        <f aca="false">Depreciate!$G$21</f>
-        <v>623592.869220248</v>
+        <f aca="false">Depreciate!$G$20</f>
+        <v>617551.610863095</v>
       </c>
       <c r="E17" s="14" t="n">
-        <f aca="false">Depreciate!$H$21</f>
-        <v>2545983.89503575</v>
+        <f aca="false">Depreciate!$H$20</f>
+        <v>2521818.86160714</v>
       </c>
       <c r="F17" s="14" t="n">
-        <f aca="false">Depreciate!$I$21</f>
-        <v>2593626.12717861</v>
+        <f aca="false">Depreciate!$I$20</f>
+        <v>2569461.09375</v>
       </c>
       <c r="G17" s="14" t="n">
-        <f aca="false">Depreciate!$J$21</f>
-        <v>2641268.35932147</v>
+        <f aca="false">Depreciate!$J$20</f>
+        <v>2617103.32589286</v>
       </c>
       <c r="H17" s="14" t="n">
-        <f aca="false">Depreciate!$K$21</f>
-        <v>2688910.59146432</v>
+        <f aca="false">Depreciate!$K$20</f>
+        <v>2664745.55803571</v>
       </c>
       <c r="I17" s="14" t="n">
-        <f aca="false">Depreciate!$L$21</f>
-        <v>2733874.25217861</v>
+        <f aca="false">Depreciate!$L$20</f>
+        <v>2709709.21875</v>
       </c>
       <c r="J17" s="14" t="n">
-        <f aca="false">Depreciate!$M$21</f>
-        <v>2773480.77003575</v>
+        <f aca="false">Depreciate!$M$20</f>
+        <v>2749315.73660714</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">SUM(D12:D17)</f>
-        <v>-25431200.0503813</v>
+        <v>-25250868.4884203</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">SUM(E12:E17)</f>
-        <v>5266470.07422887</v>
+        <v>5262845.31921458</v>
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">SUM(F12:F17)</f>
-        <v>14249199.4959908</v>
+        <v>14245574.7409765</v>
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">SUM(G12:G17)</f>
-        <v>24697202.4468361</v>
+        <v>24693577.6918218</v>
       </c>
       <c r="H18" s="17" t="n">
         <f aca="false">SUM(H12:H17)</f>
-        <v>25548304.3217475</v>
+        <v>25544679.5667332</v>
       </c>
       <c r="I18" s="17" t="n">
         <f aca="false">SUM(I12:I17)</f>
-        <v>26090594.7696718</v>
+        <v>26086970.0146575</v>
       </c>
       <c r="J18" s="17" t="n">
         <f aca="false">SUM(J12:J17)</f>
-        <v>26645386.2688947</v>
+        <v>26641761.5138804</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -12337,7 +12332,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>34</v>
@@ -12373,50 +12368,50 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="14" t="n">
-        <f aca="false">-Depreciate!$G$25</f>
+        <f aca="false">-Depreciate!$G$24</f>
         <v>-47761337.7232143</v>
       </c>
       <c r="E21" s="14" t="n">
-        <f aca="false">-Depreciate!$H$25</f>
+        <f aca="false">-Depreciate!$H$24</f>
         <v>-476422.321428571</v>
       </c>
       <c r="F21" s="14" t="n">
-        <f aca="false">-Depreciate!$I$25</f>
+        <f aca="false">-Depreciate!$I$24</f>
         <v>-476422.321428571</v>
       </c>
       <c r="G21" s="14" t="n">
-        <f aca="false">-Depreciate!$J$25</f>
+        <f aca="false">-Depreciate!$J$24</f>
         <v>-476422.321428571</v>
       </c>
       <c r="H21" s="14" t="n">
-        <f aca="false">-Depreciate!$K$25</f>
+        <f aca="false">-Depreciate!$K$24</f>
         <v>-476422.321428571</v>
       </c>
       <c r="I21" s="14" t="n">
-        <f aca="false">-Depreciate!$L$25</f>
+        <f aca="false">-Depreciate!$L$24</f>
         <v>-476422.321428571</v>
       </c>
       <c r="J21" s="14" t="n">
-        <f aca="false">-Depreciate!$M$25</f>
+        <f aca="false">-Depreciate!$M$24</f>
         <v>-476422.321428571</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">-ProfLoss!D19</f>
-        <v>-0</v>
+        <v>-1208251.67143046</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">-ProfLoss!E19</f>
@@ -12445,14 +12440,13 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="14" t="n">
-        <f aca="false">-LOANS!$C$106</f>
-        <v>-1208251.67143046</v>
+        <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
@@ -12474,44 +12468,44 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="72" t="s">
-        <v>532</v>
-      </c>
-      <c r="C24" s="60" t="s">
+      <c r="B24" s="71" t="s">
+        <v>530</v>
+      </c>
+      <c r="C24" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="49" t="n">
         <f aca="false">D18+D19+D20+D21+D22+D23</f>
-        <v>3721522.16568379</v>
+        <v>3901853.72764478</v>
       </c>
       <c r="E24" s="49" t="n">
         <f aca="false">E18+E19+E20+E21+E22+E23</f>
-        <v>3671265.55445217</v>
+        <v>3667640.79943788</v>
       </c>
       <c r="F24" s="49" t="n">
         <f aca="false">F18+F19+F20+F21+F22+F23</f>
-        <v>12858634.5572467</v>
+        <v>12855009.8022324</v>
       </c>
       <c r="G24" s="49" t="n">
         <f aca="false">G18+G19+G20+G21+G22+G23</f>
-        <v>23508012.7866637</v>
+        <v>23504388.0316494</v>
       </c>
       <c r="H24" s="49" t="n">
         <f aca="false">H18+H19+H20+H21+H22+H23</f>
-        <v>24560489.9401469</v>
+        <v>24556865.1851326</v>
       </c>
       <c r="I24" s="49" t="n">
         <f aca="false">I18+I19+I20+I21+I22+I23</f>
-        <v>25303098.2165499</v>
+        <v>25299473.4615357</v>
       </c>
       <c r="J24" s="49" t="n">
         <f aca="false">J18+J19+J20+J21+J22+J23</f>
-        <v>26060322.4444376</v>
+        <v>26056697.6894233</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>34</v>
@@ -12549,36 +12543,36 @@
       <c r="B26" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">D24+D25</f>
-        <v>3721522.16568379</v>
+        <v>3901853.72764478</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">E24+E25</f>
-        <v>833883.93856851</v>
+        <v>830259.183554219</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">F24+F25</f>
-        <v>10021252.9413631</v>
+        <v>10017628.1863488</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">G24+G25</f>
-        <v>20670631.1707801</v>
+        <v>20667006.4157658</v>
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">H24+H25</f>
-        <v>21723108.3242633</v>
+        <v>21719483.569249</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">I24+I25</f>
-        <v>22465716.6006663</v>
+        <v>22462091.845652</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">J24+J25</f>
-        <v>23222940.828554</v>
+        <v>23219316.0735397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12590,36 +12584,36 @@
       </c>
       <c r="D27" s="22" t="n">
         <f aca="false">D26</f>
-        <v>3721522.16568379</v>
+        <v>3901853.72764478</v>
       </c>
       <c r="E27" s="22" t="n">
         <f aca="false">D27+E26</f>
-        <v>4555406.1042523</v>
+        <v>4732112.911199</v>
       </c>
       <c r="F27" s="22" t="n">
         <f aca="false">E27+F26</f>
-        <v>14576659.0456154</v>
+        <v>14749741.0975478</v>
       </c>
       <c r="G27" s="22" t="n">
         <f aca="false">F27+G26</f>
-        <v>35247290.2163954</v>
+        <v>35416747.5133135</v>
       </c>
       <c r="H27" s="22" t="n">
         <f aca="false">G27+H26</f>
-        <v>56970398.5406587</v>
+        <v>57136231.0825625</v>
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">H27+I26</f>
-        <v>79436115.141325</v>
+        <v>79598322.9282145</v>
       </c>
       <c r="J27" s="22" t="n">
         <f aca="false">I27+J26</f>
-        <v>102659055.969879</v>
+        <v>102817639.001754</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>61</v>
@@ -12630,32 +12624,32 @@
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">IFERROR(E18/-(E22+E25),0)</f>
-        <v>1.33120626989293</v>
+        <v>1.33029004013488</v>
       </c>
       <c r="F29" s="21" t="n">
         <f aca="false">IFERROR(F18/-(F22+F25),0)</f>
-        <v>3.79824269023568</v>
+        <v>3.7972764816258</v>
       </c>
       <c r="G29" s="21" t="n">
         <f aca="false">IFERROR(G18/-(G22+G25),0)</f>
-        <v>6.95666654060938</v>
+        <v>6.95564552569969</v>
       </c>
       <c r="H29" s="21" t="n">
         <f aca="false">IFERROR(H18/-(H22+H25),0)</f>
-        <v>7.6291522787647</v>
+        <v>7.62806986610713</v>
       </c>
       <c r="I29" s="21" t="n">
         <f aca="false">IFERROR(I18/-(I22+I25),0)</f>
-        <v>8.28679074211933</v>
+        <v>8.285639461876</v>
       </c>
       <c r="J29" s="21" t="n">
         <f aca="false">IFERROR(J18/-(J22+J25),0)</f>
-        <v>9.04452721292065</v>
+        <v>9.04329682372545</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>61</v>
@@ -12666,50 +12660,50 @@
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">IFERROR((E18+E21)/-(E22+E25),0)</f>
-        <v>1.21078094278319</v>
+        <v>1.20986471302515</v>
       </c>
       <c r="F30" s="21" t="n">
         <f aca="false">IFERROR((F18+F21)/-(F22+F25),0)</f>
-        <v>3.67124835624939</v>
+        <v>3.67028214763951</v>
       </c>
       <c r="G30" s="21" t="n">
         <f aca="false">IFERROR((G18+G21)/-(G22+G25),0)</f>
-        <v>6.82246870059831</v>
+        <v>6.82144768568862</v>
       </c>
       <c r="H30" s="21" t="n">
         <f aca="false">IFERROR((H18+H21)/-(H22+H25),0)</f>
-        <v>7.48688458093995</v>
+        <v>7.48580216828238</v>
       </c>
       <c r="I30" s="21" t="n">
         <f aca="false">IFERROR((I18+I21)/-(I22+I25),0)</f>
-        <v>8.13547138288638</v>
+        <v>8.13432010264305</v>
       </c>
       <c r="J30" s="21" t="n">
         <f aca="false">IFERROR((J18+J21)/-(J22+J25),0)</f>
-        <v>8.88281011084832</v>
+        <v>8.88157972165312</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="26" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D31" s="77" t="n">
         <f aca="false">MIN(E30:J30)</f>
-        <v>1.21078094278319</v>
+        <v>1.20986471302515</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="26" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D32" s="77" t="n">
         <f aca="false">AVERAGE(E30:J30)</f>
-        <v>6.03494401238425</v>
+        <v>6.03388275648864</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -12750,20 +12744,20 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C4" s="22" t="n">
         <f aca="false">CostTotal!C26</f>
@@ -12790,16 +12784,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">CostTotal!F22</f>
-        <v>9682386.55827227</v>
+        <v>9658221.52484367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">CostTotal!G22</f>
@@ -12808,7 +12802,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">C4-C8</f>
@@ -12817,41 +12811,41 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="26" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C10" s="23" t="n">
         <f aca="false">IFERROR(C7/C9,0)</f>
-        <v>0.298419434889006</v>
+        <v>0.297674647890838</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">C10*C4</f>
-        <v>91889192.152237</v>
+        <v>91659857.6398497</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="C12" s="62" t="n">
+        <v>544</v>
+      </c>
+      <c r="C12" s="61" t="n">
         <f aca="false">C10*ProdPlan!F13</f>
-        <v>792.751228782644</v>
+        <v>790.77270212201</v>
       </c>
       <c r="D12" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">1-C10</f>
-        <v>0.701580565110994</v>
+        <v>0.702325352109162</v>
       </c>
     </row>
   </sheetData>
@@ -12881,12 +12875,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12931,28 +12925,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C6" s="20"/>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="59" t="n">
+      <c r="E6" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="59" t="n">
+      <c r="F6" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="59" t="n">
+      <c r="G6" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="59" t="n">
+      <c r="I6" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="59" t="n">
+      <c r="J6" s="72" t="n">
         <v>7</v>
       </c>
     </row>
@@ -12965,36 +12959,36 @@
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-25431200.0503813</v>
+        <v>-25250868.4884203</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>5266470.07422887</v>
+        <v>5262845.31921458</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>14249199.4959908</v>
+        <v>14245574.7409765</v>
       </c>
       <c r="G7" s="14" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>24697202.4468361</v>
+        <v>24693577.6918218</v>
       </c>
       <c r="H7" s="14" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>25548304.3217475</v>
+        <v>25544679.5667332</v>
       </c>
       <c r="I7" s="14" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>26090594.7696718</v>
+        <v>26086970.0146575</v>
       </c>
       <c r="J7" s="14" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>26645386.2688947</v>
+        <v>26641761.5138804</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -13029,47 +13023,47 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="72" t="s">
-        <v>552</v>
-      </c>
-      <c r="C9" s="60" t="s">
+      <c r="B9" s="71" t="s">
+        <v>550</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="49" t="n">
         <f aca="false">D7+D8</f>
-        <v>-73192537.7735956</v>
+        <v>-73012206.2116346</v>
       </c>
       <c r="E9" s="49" t="n">
         <f aca="false">E7+E8</f>
-        <v>4790047.7528003</v>
+        <v>4786422.99778601</v>
       </c>
       <c r="F9" s="49" t="n">
         <f aca="false">F7+F8</f>
-        <v>13772777.1745622</v>
+        <v>13769152.4195479</v>
       </c>
       <c r="G9" s="49" t="n">
         <f aca="false">G7+G8</f>
-        <v>24220780.1254075</v>
+        <v>24217155.3703932</v>
       </c>
       <c r="H9" s="49" t="n">
         <f aca="false">H7+H8</f>
-        <v>25071882.000319</v>
+        <v>25068257.2453047</v>
       </c>
       <c r="I9" s="49" t="n">
         <f aca="false">I7+I8</f>
-        <v>25614172.4482432</v>
+        <v>25610547.6932289</v>
       </c>
       <c r="J9" s="49" t="n">
         <f aca="false">J7+J8</f>
-        <v>26168963.9474661</v>
+        <v>26165339.1924519</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.112983406727648</v>
@@ -13101,7 +13095,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="78" t="n">
@@ -13135,115 +13129,115 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">D9*D11</f>
-        <v>-65762469.8905382</v>
+        <v>-65600444.5082451</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">E9*E11</f>
-        <v>3866895.75038685</v>
+        <v>3863969.5687527</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">F9*F11</f>
-        <v>9989769.15348984</v>
+        <v>9987140.02028222</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">G9*G11</f>
-        <v>15784592.2982323</v>
+        <v>15782230.0588748</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">H9*H11</f>
-        <v>14680589.2387607</v>
+        <v>14678466.7997889</v>
       </c>
       <c r="I12" s="14" t="n">
         <f aca="false">I9*I11</f>
-        <v>13475602.4978743</v>
+        <v>13473695.5161897</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">J9*J11</f>
-        <v>12369886.1341844</v>
+        <v>12368172.7378542</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">D9</f>
-        <v>-73192537.7735956</v>
+        <v>-73012206.2116346</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">D13+E9</f>
-        <v>-68402490.0207953</v>
+        <v>-68225783.2138486</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">E13+F9</f>
-        <v>-54629712.8462331</v>
+        <v>-54456630.7943006</v>
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">F13+G9</f>
-        <v>-30408932.7208256</v>
+        <v>-30239475.4239074</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">G13+H9</f>
-        <v>-5337050.72050662</v>
+        <v>-5171218.17860279</v>
       </c>
       <c r="I13" s="14" t="n">
         <f aca="false">H13+I9</f>
-        <v>20277121.7277366</v>
+        <v>20439329.5146261</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">I13+J9</f>
-        <v>46446085.6752027</v>
+        <v>46604668.707078</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D12</f>
-        <v>-65762469.8905382</v>
+        <v>-65600444.5082451</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">D14+E12</f>
-        <v>-61895574.1401514</v>
+        <v>-61736474.9394924</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">E14+F12</f>
-        <v>-51905804.9866615</v>
+        <v>-51749334.9192101</v>
       </c>
       <c r="G14" s="14" t="n">
         <f aca="false">F14+G12</f>
-        <v>-36121212.6884292</v>
+        <v>-35967104.8603353</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">G14+H12</f>
-        <v>-21440623.4496685</v>
+        <v>-21288638.0605465</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">H14+I12</f>
-        <v>-7965020.9517942</v>
+        <v>-7814942.54435677</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">I14+J12</f>
-        <v>4404865.18239016</v>
+        <v>4553230.19349745</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="79" t="str">
@@ -13268,7 +13262,7 @@
       </c>
       <c r="I15" s="79" t="n">
         <f aca="false">IF(AND(H13&lt;0,I13&gt;=0),H6-H13/I9,"")</f>
-        <v>5.20836319156088</v>
+        <v>5.2019175161947</v>
       </c>
       <c r="J15" s="79" t="str">
         <f aca="false">IF(AND(I13&lt;0,J13&gt;=0),I6-I13/J9,"")</f>
@@ -13277,7 +13271,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="79" t="str">
@@ -13306,27 +13300,27 @@
       </c>
       <c r="J16" s="79" t="n">
         <f aca="false">IF(AND(I14&lt;0,J14&gt;=0),I6-I14/J12,"")</f>
-        <v>6.64390414474251</v>
+        <v>6.631859104008</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="17" t="n">
         <f aca="false">SUM(D12:J12)</f>
-        <v>4404865.18239016</v>
+        <v>4553230.19349745</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="18" t="n">
         <f aca="false">IFERROR(IRR(D9:J9),"-")</f>
-        <v>0.131878108331531</v>
+        <v>0.132548684120501</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13336,17 +13330,17 @@
       <c r="C20" s="16"/>
       <c r="D20" s="80" t="n">
         <f aca="false">IFERROR(SUM(E12:J12)/-D12,0)</f>
-        <v>1.06698144381928</v>
+        <v>1.06940852653712</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="81" t="n">
         <f aca="false">IF(COUNT(E15:J15)&gt;0,SUM(E15:J15),"&gt; 7")</f>
-        <v>5.20836319156088</v>
+        <v>5.2019175161947</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13356,7 +13350,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="81" t="n">
         <f aca="false">IF(COUNT(E16:J16)&gt;0,SUM(E16:J16),"&gt; 7")</f>
-        <v>6.64390414474251</v>
+        <v>6.631859104008</v>
       </c>
     </row>
   </sheetData>
@@ -15456,266 +15450,220 @@
         <v>297763.950892857</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="49" t="n">
+        <f aca="false">SUM(D7:D19)</f>
+        <v>50619871.6517857</v>
+      </c>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="49" t="n">
+        <f aca="false">SUM(G7:G19)</f>
+        <v>617551.610863095</v>
+      </c>
+      <c r="H20" s="49" t="n">
+        <f aca="false">SUM(H7:H19)</f>
+        <v>2521818.86160714</v>
+      </c>
+      <c r="I20" s="49" t="n">
+        <f aca="false">SUM(I7:I19)</f>
+        <v>2569461.09375</v>
+      </c>
+      <c r="J20" s="49" t="n">
+        <f aca="false">SUM(J7:J19)</f>
+        <v>2617103.32589286</v>
+      </c>
+      <c r="K20" s="49" t="n">
+        <f aca="false">SUM(K7:K19)</f>
+        <v>2664745.55803571</v>
+      </c>
+      <c r="L20" s="49" t="n">
+        <f aca="false">SUM(L7:L19)</f>
+        <v>2709709.21875</v>
+      </c>
+      <c r="M20" s="49" t="n">
+        <f aca="false">SUM(M7:M19)</f>
+        <v>2749315.73660714</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D20" s="14" t="n">
-        <f aca="false">LOANS!$C$106</f>
-        <v>1208251.67143046</v>
-      </c>
-      <c r="E20" s="59" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <f aca="false">1/E20</f>
-        <v>0.02</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <f aca="false">D20/E20*3/12</f>
-        <v>6041.2583571523</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-      <c r="K20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-      <c r="M20" s="14" t="n">
-        <f aca="false">D20/E20</f>
-        <v>24165.0334286092</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="D21" s="49" t="n">
-        <f aca="false">SUM(D7:D20)</f>
-        <v>51828123.3232162</v>
-      </c>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="49" t="n">
-        <f aca="false">SUM(G7:G20)</f>
-        <v>623592.869220248</v>
-      </c>
-      <c r="H21" s="49" t="n">
-        <f aca="false">SUM(H7:H20)</f>
-        <v>2545983.89503575</v>
-      </c>
-      <c r="I21" s="49" t="n">
-        <f aca="false">SUM(I7:I20)</f>
-        <v>2593626.12717861</v>
-      </c>
-      <c r="J21" s="49" t="n">
-        <f aca="false">SUM(J7:J20)</f>
-        <v>2641268.35932147</v>
-      </c>
-      <c r="K21" s="49" t="n">
-        <f aca="false">SUM(K7:K20)</f>
-        <v>2688910.59146432</v>
-      </c>
-      <c r="L21" s="49" t="n">
-        <f aca="false">SUM(L7:L20)</f>
-        <v>2733874.25217861</v>
-      </c>
-      <c r="M21" s="49" t="n">
-        <f aca="false">SUM(M7:M20)</f>
-        <v>2773480.77003575</v>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="14" t="n">
+        <f aca="false">G20-G22</f>
+        <v>614873.039434524</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <f aca="false">H20-H22</f>
+        <v>2511104.57589286</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <f aca="false">I20-I22</f>
+        <v>2558746.80803571</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <f aca="false">J20-J22</f>
+        <v>2606389.04017857</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <f aca="false">K20-K22</f>
+        <v>2654031.27232143</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <f aca="false">L20-L22</f>
+        <v>2701673.50446428</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <f aca="false">M20-M22</f>
+        <v>2749315.73660714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="14" t="n">
-        <f aca="false">G21-G23</f>
-        <v>620914.297791676</v>
+        <v>2678.57142857143</v>
       </c>
       <c r="H22" s="14" t="n">
-        <f aca="false">H21-H23</f>
-        <v>2535269.60932147</v>
+        <v>10714.2857142857</v>
       </c>
       <c r="I22" s="14" t="n">
-        <f aca="false">I21-I23</f>
-        <v>2582911.84146432</v>
+        <v>10714.2857142857</v>
       </c>
       <c r="J22" s="14" t="n">
-        <f aca="false">J21-J23</f>
-        <v>2630554.07360718</v>
+        <v>10714.2857142857</v>
       </c>
       <c r="K22" s="14" t="n">
-        <f aca="false">K21-K23</f>
-        <v>2678196.30575004</v>
+        <v>10714.2857142857</v>
       </c>
       <c r="L22" s="14" t="n">
-        <f aca="false">L21-L23</f>
-        <v>2725838.53789289</v>
+        <v>8035.71428571429</v>
       </c>
       <c r="M22" s="14" t="n">
-        <f aca="false">M21-M23</f>
-        <v>2773480.77003575</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14" t="n">
+        <v>47761337.7232143</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>476422.321428571</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="29" t="s">
         <v>221</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14" t="n">
-        <v>2678.57142857143</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>10714.2857142857</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>10714.2857142857</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>10714.2857142857</v>
-      </c>
-      <c r="K23" s="14" t="n">
-        <v>10714.2857142857</v>
-      </c>
-      <c r="L23" s="14" t="n">
-        <v>8035.71428571429</v>
-      </c>
-      <c r="M23" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="14" t="n">
-        <v>47761337.7232143</v>
+        <f aca="false">SUM($G$20:G20)</f>
+        <v>617551.610863095</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>476422.321428571</v>
+        <f aca="false">SUM($G$20:H20)</f>
+        <v>3139370.47247024</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>476422.321428571</v>
+        <f aca="false">SUM($G$20:I20)</f>
+        <v>5708831.56622024</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>476422.321428571</v>
+        <f aca="false">SUM($G$20:J20)</f>
+        <v>8325934.89211309</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>476422.321428571</v>
+        <f aca="false">SUM($G$20:K20)</f>
+        <v>10990680.4501488</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>476422.321428571</v>
+        <f aca="false">SUM($G$20:L20)</f>
+        <v>13700389.6688988</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>476422.321428571</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">SUM($G$20:M20)</f>
+        <v>16449705.4055059</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
       <c r="G26" s="14" t="n">
-        <f aca="false">SUM($G$21:G21)</f>
-        <v>623592.869220248</v>
+        <f aca="false">G24-G20</f>
+        <v>47143786.1123512</v>
       </c>
       <c r="H26" s="14" t="n">
-        <f aca="false">SUM($G$21:H21)</f>
-        <v>3169576.764256</v>
+        <f aca="false">G26+H24-H20</f>
+        <v>45098389.5721726</v>
       </c>
       <c r="I26" s="14" t="n">
-        <f aca="false">SUM($G$21:I21)</f>
-        <v>5763202.89143461</v>
+        <f aca="false">H26+I24-I20</f>
+        <v>43005350.7998512</v>
       </c>
       <c r="J26" s="14" t="n">
-        <f aca="false">SUM($G$21:J21)</f>
-        <v>8404471.25075607</v>
+        <f aca="false">I26+J24-J20</f>
+        <v>40864669.7953869</v>
       </c>
       <c r="K26" s="14" t="n">
-        <f aca="false">SUM($G$21:K21)</f>
-        <v>11093381.8422204</v>
+        <f aca="false">J26+K24-K20</f>
+        <v>38676346.5587798</v>
       </c>
       <c r="L26" s="14" t="n">
-        <f aca="false">SUM($G$21:L21)</f>
-        <v>13827256.094399</v>
+        <f aca="false">K26+L24-L20</f>
+        <v>36443059.6614584</v>
       </c>
       <c r="M26" s="14" t="n">
-        <f aca="false">SUM($G$21:M21)</f>
-        <v>16600736.8644348</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14" t="n">
-        <f aca="false">G25+$D$20-G21</f>
-        <v>48345996.5254245</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <f aca="false">G27+H25-H21</f>
-        <v>46276434.9518173</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <f aca="false">H27+I25-I21</f>
-        <v>44159231.1460673</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <f aca="false">I27+J25-J21</f>
-        <v>41994385.1081744</v>
-      </c>
-      <c r="K27" s="14" t="n">
-        <f aca="false">J27+K25-K21</f>
-        <v>39781896.8381387</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <f aca="false">K27+L25-L21</f>
-        <v>37524444.9073886</v>
-      </c>
-      <c r="M27" s="14" t="n">
-        <f aca="false">L27+M25-M21</f>
-        <v>35227386.4587814</v>
-      </c>
-    </row>
+        <f aca="false">L26+M24-M20</f>
+        <v>34170166.2462798</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B5:B6"/>
@@ -15757,33 +15705,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>229</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15791,13 +15739,13 @@
         <v>11</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="62" t="n">
+        <v>230</v>
+      </c>
+      <c r="D5" s="61" t="n">
         <v>2656.5</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F5" s="30" t="n">
         <f aca="false">F20</f>
@@ -15870,23 +15818,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
+        <v>232</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.101637492941841</v>
@@ -15912,192 +15860,192 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
+        <v>234</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="62" t="n">
+        <v>230</v>
+      </c>
+      <c r="D13" s="61" t="n">
         <f aca="false">$D$5*D11</f>
         <v>270.000000000001</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="61" t="n">
         <f aca="false">$D$5*E11</f>
         <v>2204.125</v>
       </c>
-      <c r="F13" s="62" t="n">
+      <c r="F13" s="61" t="n">
         <f aca="false">$D$5*F11</f>
         <v>2656.5</v>
       </c>
-      <c r="G13" s="62" t="n">
+      <c r="G13" s="61" t="n">
         <f aca="false">$D$5*G11</f>
         <v>2656.5</v>
       </c>
-      <c r="H13" s="62" t="n">
+      <c r="H13" s="61" t="n">
         <f aca="false">$D$5*H11</f>
         <v>2656.5</v>
       </c>
-      <c r="I13" s="62" t="n">
+      <c r="I13" s="61" t="n">
         <f aca="false">$D$5*I11</f>
         <v>2656.5</v>
       </c>
-      <c r="J13" s="62" t="n">
+      <c r="J13" s="61" t="n">
         <f aca="false">$D$5*J11</f>
         <v>2656.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
+        <v>235</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="62" t="n">
+        <v>230</v>
+      </c>
+      <c r="D15" s="61" t="n">
         <v>250</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="61" t="n">
         <v>2154.125</v>
       </c>
-      <c r="F15" s="62" t="n">
+      <c r="F15" s="61" t="n">
         <v>2623.29375</v>
       </c>
-      <c r="G15" s="62" t="n">
+      <c r="G15" s="61" t="n">
         <v>2656.5</v>
       </c>
-      <c r="H15" s="62" t="n">
+      <c r="H15" s="61" t="n">
         <v>2656.5</v>
       </c>
-      <c r="I15" s="62" t="n">
+      <c r="I15" s="61" t="n">
         <v>2656.5</v>
       </c>
-      <c r="J15" s="62" t="n">
+      <c r="J15" s="61" t="n">
         <v>2656.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="62" t="n">
+        <v>230</v>
+      </c>
+      <c r="D16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
+        <v>238</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D18" s="62" t="n">
+        <v>230</v>
+      </c>
+      <c r="D18" s="61" t="n">
         <f aca="false">0+D13-D15-D16</f>
         <v>20.0000000000006</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="61" t="n">
         <f aca="false">D18+E13-E15-E16</f>
         <v>70</v>
       </c>
-      <c r="F18" s="62" t="n">
+      <c r="F18" s="61" t="n">
         <f aca="false">E18+F13-F15-F16</f>
         <v>103.20625</v>
       </c>
-      <c r="G18" s="62" t="n">
+      <c r="G18" s="61" t="n">
         <f aca="false">F18+G13-G15-G16</f>
         <v>103.20625</v>
       </c>
-      <c r="H18" s="62" t="n">
+      <c r="H18" s="61" t="n">
         <f aca="false">G18+H13-H15-H16</f>
         <v>103.20625</v>
       </c>
-      <c r="I18" s="62" t="n">
+      <c r="I18" s="61" t="n">
         <f aca="false">H18+I13-I15-I16</f>
         <v>103.20625</v>
       </c>
-      <c r="J18" s="62" t="n">
+      <c r="J18" s="61" t="n">
         <f aca="false">I18+J13-J15-J16</f>
         <v>103.20625</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
+        <v>239</v>
+      </c>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>113325</v>
@@ -16159,10 +16107,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16207,20 +16155,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
+        <v>243</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -16292,20 +16240,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
+        <v>245</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
@@ -16377,9 +16325,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="63" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="17" t="n">
@@ -16413,10 +16361,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D15" s="15" t="n">
         <f aca="false">IFERROR(D8/D14,0)</f>
@@ -16488,43 +16436,43 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="H5" s="19" t="s">
         <v>256</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -16535,16 +16483,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D7" s="30" t="n">
         <f aca="false">IFERROR(F7/E7,0)</f>
         <v>51900.12854645</v>
       </c>
-      <c r="E7" s="62" t="n">
+      <c r="E7" s="61" t="n">
         <v>5000</v>
       </c>
       <c r="F7" s="14" t="n">
@@ -16554,13 +16502,13 @@
         <f aca="false">IFERROR(F7/$F$24,0)</f>
         <v>0.978119226650116</v>
       </c>
-      <c r="H7" s="64" t="s">
-        <v>261</v>
+      <c r="H7" s="63" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -16577,7 +16525,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -16588,16 +16536,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D11" s="30" t="n">
         <f aca="false">IFERROR(F11/E11,0)</f>
         <v>211.573495816644</v>
       </c>
-      <c r="E11" s="62" t="n">
+      <c r="E11" s="61" t="n">
         <v>449.61</v>
       </c>
       <c r="F11" s="14" t="n">
@@ -16607,22 +16555,22 @@
         <f aca="false">IFERROR(F11/$F$24,0)</f>
         <v>0.000358550705956928</v>
       </c>
-      <c r="H11" s="64" t="s">
-        <v>265</v>
+      <c r="H11" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D12" s="30" t="n">
         <f aca="false">IFERROR(F12/E12,0)</f>
         <v>65.6444551752533</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="61" t="n">
         <v>9800</v>
       </c>
       <c r="F12" s="14" t="n">
@@ -16632,22 +16580,22 @@
         <f aca="false">IFERROR(F12/$F$24,0)</f>
         <v>0.00242480870154196</v>
       </c>
-      <c r="H12" s="64" t="s">
-        <v>265</v>
+      <c r="H12" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D13" s="30" t="n">
         <f aca="false">IFERROR(F13/E13,0)</f>
         <v>998.834695652235</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="61" t="n">
         <v>2000</v>
       </c>
       <c r="F13" s="14" t="n">
@@ -16657,22 +16605,22 @@
         <f aca="false">IFERROR(F13/$F$24,0)</f>
         <v>0.00752968786339928</v>
       </c>
-      <c r="H13" s="64" t="s">
-        <v>265</v>
+      <c r="H13" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D14" s="30" t="n">
         <f aca="false">IFERROR(F14/E14,0)</f>
         <v>493.614850250894</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="61" t="n">
         <v>3769.4</v>
       </c>
       <c r="F14" s="14" t="n">
@@ -16682,22 +16630,22 @@
         <f aca="false">IFERROR(F14/$F$24,0)</f>
         <v>0.00701316087046572</v>
       </c>
-      <c r="H14" s="64" t="s">
-        <v>265</v>
+      <c r="H14" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D15" s="30" t="n">
         <f aca="false">IFERROR(F15/E15,0)</f>
         <v>947.522077959676</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="61" t="n">
         <v>163.5</v>
       </c>
       <c r="F15" s="14" t="n">
@@ -16707,22 +16655,22 @@
         <f aca="false">IFERROR(F15/$F$24,0)</f>
         <v>0.000583929549508851</v>
       </c>
-      <c r="H15" s="64" t="s">
-        <v>265</v>
+      <c r="H15" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D16" s="30" t="n">
         <f aca="false">IFERROR(F16/E16,0)</f>
         <v>451.48272768016</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="61" t="n">
         <v>2098.19</v>
       </c>
       <c r="F16" s="14" t="n">
@@ -16732,22 +16680,22 @@
         <f aca="false">IFERROR(F16/$F$24,0)</f>
         <v>0.00357058446427166</v>
       </c>
-      <c r="H16" s="64" t="s">
-        <v>265</v>
+      <c r="H16" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D17" s="30" t="n">
         <f aca="false">IFERROR(F17/E17,0)</f>
         <v>381.587912097875</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="61" t="n">
         <v>5.99</v>
       </c>
       <c r="F17" s="14" t="n">
@@ -16757,22 +16705,22 @@
         <f aca="false">IFERROR(F17/$F$24,0)</f>
         <v>8.61538697017103E-006</v>
       </c>
-      <c r="H17" s="64" t="s">
-        <v>265</v>
+      <c r="H17" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D18" s="30" t="n">
         <f aca="false">IFERROR(F18/E18,0)</f>
         <v>213.462544886436</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="61" t="n">
         <v>6.79</v>
       </c>
       <c r="F18" s="14" t="n">
@@ -16782,22 +16730,22 @@
         <f aca="false">IFERROR(F18/$F$24,0)</f>
         <v>5.46317125952756E-006</v>
       </c>
-      <c r="H18" s="64" t="s">
-        <v>265</v>
+      <c r="H18" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D19" s="30" t="n">
         <f aca="false">IFERROR(F19/E19,0)</f>
         <v>965.304074663435</v>
       </c>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="61" t="n">
         <v>19.33</v>
       </c>
       <c r="F19" s="14" t="n">
@@ -16807,22 +16755,22 @@
         <f aca="false">IFERROR(F19/$F$24,0)</f>
         <v>7.03314144020317E-005</v>
       </c>
-      <c r="H19" s="64" t="s">
-        <v>265</v>
+      <c r="H19" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D20" s="30" t="n">
         <f aca="false">IFERROR(F20/E20,0)</f>
         <v>14.6401302908838</v>
       </c>
-      <c r="E20" s="62" t="n">
+      <c r="E20" s="61" t="n">
         <v>4000</v>
       </c>
       <c r="F20" s="14" t="n">
@@ -16832,22 +16780,22 @@
         <f aca="false">IFERROR(F20/$F$24,0)</f>
         <v>0.000220728438548821</v>
       </c>
-      <c r="H20" s="64" t="s">
-        <v>265</v>
+      <c r="H20" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D21" s="30" t="n">
         <f aca="false">IFERROR(F21/E21,0)</f>
         <v>0.236974459201518</v>
       </c>
-      <c r="E21" s="62" t="n">
+      <c r="E21" s="61" t="n">
         <v>106260</v>
       </c>
       <c r="F21" s="14" t="n">
@@ -16857,13 +16805,13 @@
         <f aca="false">IFERROR(F21/$F$24,0)</f>
         <v>9.49127835589796E-005</v>
       </c>
-      <c r="H21" s="64" t="s">
-        <v>265</v>
+      <c r="H21" s="63" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -16880,11 +16828,11 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
+        <v>277</v>
+      </c>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="17" t="n">
         <f aca="false">F8+F22</f>
         <v>265305737.441634</v>
@@ -16893,11 +16841,11 @@
         <f aca="false">IFERROR(F24/$F$24,0)</f>
         <v>1</v>
       </c>
-      <c r="H24" s="65"/>
+      <c r="H24" s="64"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -16908,22 +16856,22 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G27" s="19"/>
       <c r="H27" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -16932,13 +16880,13 @@
         <v>945456.722527941</v>
       </c>
       <c r="G28" s="13"/>
-      <c r="H28" s="66" t="s">
-        <v>284</v>
+      <c r="H28" s="65" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
@@ -16947,13 +16895,13 @@
         <v>617586.499460136</v>
       </c>
       <c r="G29" s="13"/>
-      <c r="H29" s="66" t="s">
-        <v>286</v>
+      <c r="H29" s="65" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="13" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -16967,7 +16915,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
